--- a/Historical_data_AC.xlsx
+++ b/Historical_data_AC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6450e5a01e7561fa/Desktop/ONG_proyectopersonal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{F31FDF5D-312F-4427-AC18-8DFE64B91489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{F7B9CE97-AC28-4472-9E04-A2F306659678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{34D6BA04-1AFF-4A7C-9B19-3A12058CBEFE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{34D6BA04-1AFF-4A7C-9B19-3A12058CBEFE}"/>
   </bookViews>
   <sheets>
     <sheet name="All containers" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="55">
   <si>
     <t>Numero Contenedor</t>
   </si>
@@ -115,9 +115,6 @@
   </si>
   <si>
     <t>Siria</t>
-  </si>
-  <si>
-    <t>Malaga</t>
   </si>
   <si>
     <t>Ghana</t>
@@ -260,10 +257,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -583,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DDCD075-27BE-40FA-AF83-D2B889D59367}">
-  <dimension ref="A1:D428"/>
+  <dimension ref="A1:C428"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -1932,7 +1925,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -1944,7 +1937,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -1956,7 +1949,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -1968,7 +1961,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116">
         <f t="shared" si="1"/>
         <v>115</v>
@@ -1980,7 +1973,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -1992,7 +1985,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -2004,7 +1997,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -2016,7 +2009,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -2028,7 +2021,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -2040,7 +2033,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -2052,7 +2045,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -2064,7 +2057,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124">
         <f t="shared" si="1"/>
         <v>123</v>
@@ -2076,7 +2069,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125">
         <f t="shared" si="1"/>
         <v>124</v>
@@ -2088,7 +2081,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -2100,7 +2093,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -2112,22 +2105,19 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128">
         <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C128">
         <v>2019</v>
       </c>
-      <c r="D128" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -2139,7 +2129,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -2151,7 +2141,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -2163,7 +2153,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132">
         <f t="shared" ref="A132:A195" si="2">A131+1</f>
         <v>131</v>
@@ -2175,7 +2165,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133">
         <f t="shared" si="2"/>
         <v>132</v>
@@ -2187,7 +2177,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134">
         <f t="shared" si="2"/>
         <v>133</v>
@@ -2199,7 +2189,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135">
         <f t="shared" si="2"/>
         <v>134</v>
@@ -2211,7 +2201,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -2223,7 +2213,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -2235,7 +2225,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -2247,7 +2237,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -2259,7 +2249,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -2271,22 +2261,19 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141">
         <f t="shared" si="2"/>
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C141">
         <v>2019</v>
       </c>
-      <c r="D141" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -2298,22 +2285,19 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143">
         <f t="shared" si="2"/>
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C143">
         <v>2019</v>
       </c>
-      <c r="D143" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -2325,7 +2309,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -2337,7 +2321,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -2349,7 +2333,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -2361,7 +2345,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -2373,7 +2357,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -2385,46 +2369,43 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150">
         <f t="shared" si="2"/>
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C150">
         <v>2020</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C151">
         <v>2020</v>
       </c>
-      <c r="D151" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152">
         <f t="shared" si="2"/>
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C152">
         <v>2020</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -2436,7 +2417,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -2448,19 +2429,19 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155">
         <f t="shared" si="2"/>
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C155">
         <v>2020</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -2472,7 +2453,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -2484,7 +2465,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -2496,7 +2477,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -2508,13 +2489,13 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160">
         <f t="shared" si="2"/>
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C160">
         <v>2020</v>
@@ -2586,7 +2567,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C166">
         <v>2020</v>
@@ -2670,7 +2651,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C173">
         <v>2020</v>
@@ -2712,7 +2693,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -2724,7 +2705,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -2736,7 +2717,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -2748,7 +2729,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -2760,22 +2741,19 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181">
         <f t="shared" si="2"/>
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C181">
         <v>2021</v>
       </c>
-      <c r="D181" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -2787,7 +2765,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -2799,34 +2777,31 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184">
         <f t="shared" si="2"/>
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C184">
         <v>2021</v>
       </c>
-      <c r="D184" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185">
         <f t="shared" si="2"/>
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C185">
         <v>2021</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -2838,7 +2813,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -2850,7 +2825,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -2862,19 +2837,19 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189">
         <f t="shared" si="2"/>
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C189">
         <v>2021</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -2886,7 +2861,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -2898,13 +2873,13 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192">
         <f t="shared" si="2"/>
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C192">
         <v>2021</v>
@@ -2940,7 +2915,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C195">
         <v>2021</v>
@@ -3060,7 +3035,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C205">
         <v>2021</v>
@@ -3120,7 +3095,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C210">
         <v>2022</v>
@@ -3132,7 +3107,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C211">
         <v>2022</v>
@@ -3144,7 +3119,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C212">
         <v>2022</v>
@@ -3156,7 +3131,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C213">
         <v>2022</v>
@@ -3168,7 +3143,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C214">
         <v>2022</v>
@@ -3180,7 +3155,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C215">
         <v>2022</v>
@@ -3216,7 +3191,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C218">
         <v>2022</v>
@@ -3252,7 +3227,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C221">
         <v>2022</v>
@@ -3276,7 +3251,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C223">
         <v>2022</v>
@@ -3300,7 +3275,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C225">
         <v>2022</v>
@@ -3312,7 +3287,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C226">
         <v>2022</v>
@@ -3336,7 +3311,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C228">
         <v>2022</v>
@@ -3396,7 +3371,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C233">
         <v>2022</v>
@@ -3408,7 +3383,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C234">
         <v>2022</v>
@@ -3444,7 +3419,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C237">
         <v>2022</v>
@@ -3492,7 +3467,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C241">
         <v>2022</v>
@@ -3504,7 +3479,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C242">
         <v>2022</v>
@@ -3516,7 +3491,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C243">
         <v>2022</v>
@@ -3540,7 +3515,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C245">
         <v>2022</v>
@@ -3576,7 +3551,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C248">
         <v>2022</v>
@@ -3588,7 +3563,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C249">
         <v>2022</v>
@@ -3600,7 +3575,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C250">
         <v>2022</v>
@@ -3612,7 +3587,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C251">
         <v>2022</v>
@@ -3624,7 +3599,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C252">
         <v>2022</v>
@@ -3660,7 +3635,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C255">
         <v>2023</v>
@@ -3672,7 +3647,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C256">
         <v>2023</v>
@@ -3684,7 +3659,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C257">
         <v>2023</v>
@@ -3876,7 +3851,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C273">
         <v>2023</v>
@@ -3888,7 +3863,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C274">
         <v>2023</v>
@@ -3948,7 +3923,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C279">
         <v>2023</v>
@@ -3960,7 +3935,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C280">
         <v>2023</v>
@@ -3984,7 +3959,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C282">
         <v>2023</v>
@@ -4020,7 +3995,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C285">
         <v>2023</v>
@@ -4032,7 +4007,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C286">
         <v>2023</v>
@@ -4044,7 +4019,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C287">
         <v>2023</v>
@@ -4092,7 +4067,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C291">
         <v>2023</v>
@@ -4128,7 +4103,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C294">
         <v>2023</v>
@@ -4164,7 +4139,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C297">
         <v>2023</v>
@@ -4176,7 +4151,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C298">
         <v>2023</v>
@@ -4188,7 +4163,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C299">
         <v>2023</v>
@@ -4200,7 +4175,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C300">
         <v>2023</v>
@@ -4248,7 +4223,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C304">
         <v>2024</v>
@@ -4272,7 +4247,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C306">
         <v>2024</v>
@@ -4296,7 +4271,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C308">
         <v>2024</v>
@@ -4308,7 +4283,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C309">
         <v>2024</v>
@@ -4332,7 +4307,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C311">
         <v>2024</v>
@@ -4356,7 +4331,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C313">
         <v>2024</v>
@@ -4368,7 +4343,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C314">
         <v>2024</v>
@@ -4380,7 +4355,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C315">
         <v>2024</v>
@@ -4404,7 +4379,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C317">
         <v>2024</v>
@@ -4440,7 +4415,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C320">
         <v>2024</v>
@@ -4452,7 +4427,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C321">
         <v>2024</v>
@@ -4488,7 +4463,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C324">
         <v>2024</v>
@@ -4512,7 +4487,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C326">
         <v>2024</v>
@@ -4572,7 +4547,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C331">
         <v>2024</v>
@@ -4584,7 +4559,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C332">
         <v>2024</v>
@@ -4596,7 +4571,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C333">
         <v>2024</v>
@@ -4656,7 +4631,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C338">
         <v>2024</v>
@@ -4692,7 +4667,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C341">
         <v>2024</v>
@@ -4704,7 +4679,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C342">
         <v>2024</v>
@@ -4716,7 +4691,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C343">
         <v>2024</v>
@@ -4728,7 +4703,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C344">
         <v>2024</v>
@@ -4764,7 +4739,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C347">
         <v>2024</v>
@@ -4776,7 +4751,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C348">
         <v>2024</v>
@@ -4800,7 +4775,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C350">
         <v>2024</v>
@@ -4836,7 +4811,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C353">
         <v>2024</v>
@@ -4848,7 +4823,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C354">
         <v>2024</v>
@@ -4860,7 +4835,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C355">
         <v>2024</v>
@@ -4896,7 +4871,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C358">
         <v>2024</v>
@@ -5004,7 +4979,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C367">
         <v>2025</v>
@@ -5028,7 +5003,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C369">
         <v>2025</v>
@@ -5040,7 +5015,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C370">
         <v>2025</v>
@@ -5052,7 +5027,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C371">
         <v>2025</v>
@@ -5064,7 +5039,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C372">
         <v>2025</v>
@@ -5088,7 +5063,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C374">
         <v>2025</v>
@@ -5100,7 +5075,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C375">
         <v>2025</v>
@@ -5112,7 +5087,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C376">
         <v>2025</v>
@@ -5160,7 +5135,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C380">
         <v>2025</v>
@@ -5184,7 +5159,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C382">
         <v>2025</v>
@@ -5208,7 +5183,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C384">
         <v>2025</v>
@@ -5220,7 +5195,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C385">
         <v>2025</v>
@@ -5232,7 +5207,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C386">
         <v>2025</v>
@@ -5244,7 +5219,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C387">
         <v>2025</v>
@@ -5256,7 +5231,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C388">
         <v>2025</v>
@@ -5268,7 +5243,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C389">
         <v>2025</v>
@@ -5280,7 +5255,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C390">
         <v>2025</v>
@@ -5292,7 +5267,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C391">
         <v>2025</v>
@@ -5304,7 +5279,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C392">
         <v>2025</v>
@@ -5352,7 +5327,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C396">
         <v>2025</v>
@@ -5364,7 +5339,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C397">
         <v>2025</v>
@@ -5376,7 +5351,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C398">
         <v>2025</v>
@@ -5388,7 +5363,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C399">
         <v>2025</v>
@@ -5424,7 +5399,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C402">
         <v>2025</v>
@@ -5448,7 +5423,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C404">
         <v>2025</v>
@@ -5496,7 +5471,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C408">
         <v>2025</v>
@@ -5508,7 +5483,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C409">
         <v>2025</v>
@@ -5520,7 +5495,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C410">
         <v>2025</v>
@@ -5544,7 +5519,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C412">
         <v>2025</v>
@@ -5604,7 +5579,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C417">
         <v>2025</v>
@@ -5664,7 +5639,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C422">
         <v>2025</v>
@@ -5676,7 +5651,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C423">
         <v>2025</v>
@@ -5688,7 +5663,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C424">
         <v>2025</v>
@@ -5758,7 +5733,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -5781,7 +5756,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2">
         <v>116</v>
@@ -5798,7 +5773,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3">
         <v>62</v>
@@ -5815,7 +5790,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4">
         <v>175</v>
@@ -5838,7 +5813,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5">
         <v>179</v>
@@ -5855,7 +5830,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6">
         <v>78</v>
@@ -5872,7 +5847,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7">
         <v>59837</v>
@@ -5895,7 +5870,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>16</v>
@@ -5912,7 +5887,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9">
         <v>31</v>
@@ -5932,7 +5907,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10">
         <v>15</v>

--- a/Historical_data_AC.xlsx
+++ b/Historical_data_AC.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6450e5a01e7561fa/Desktop/ONG_proyectopersonal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{F7B9CE97-AC28-4472-9E04-A2F306659678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{98D57DAD-A366-43BE-B74E-2A6B22B12204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{34D6BA04-1AFF-4A7C-9B19-3A12058CBEFE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{34D6BA04-1AFF-4A7C-9B19-3A12058CBEFE}"/>
   </bookViews>
   <sheets>
     <sheet name="All containers" sheetId="1" r:id="rId1"/>
     <sheet name="Material" sheetId="2" r:id="rId2"/>
+    <sheet name="Countries coordinates" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="59">
   <si>
     <t>Numero Contenedor</t>
   </si>
@@ -205,6 +206,18 @@
   </si>
   <si>
     <t>Material enviado</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Perú</t>
   </si>
 </sst>
 </file>
@@ -5928,4 +5941,487 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE55D653-3B6D-48C5-A45F-119C8615AE3D}">
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>-8.8390000000000004</v>
+      </c>
+      <c r="C2">
+        <v>13.289400000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3">
+        <v>28.033899999999999</v>
+      </c>
+      <c r="C3">
+        <v>1.6596</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>9.3077000000000005</v>
+      </c>
+      <c r="C4">
+        <v>2.3157999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>12.238300000000001</v>
+      </c>
+      <c r="C5">
+        <v>-1.5616000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>-3.3731</v>
+      </c>
+      <c r="C6">
+        <v>29.918900000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>16.538799999999998</v>
+      </c>
+      <c r="C7">
+        <v>-23.041799999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>7.3696999999999999</v>
+      </c>
+      <c r="C8">
+        <v>12.354699999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>-0.22800000000000001</v>
+      </c>
+      <c r="C9">
+        <v>15.8277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10">
+        <v>21.521799999999999</v>
+      </c>
+      <c r="C10">
+        <v>-77.781199999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11">
+        <v>40.463700000000003</v>
+      </c>
+      <c r="C11">
+        <v>-3.7492000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12">
+        <v>9.1449999999999996</v>
+      </c>
+      <c r="C12">
+        <v>40.489699999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13">
+        <v>13.443199999999999</v>
+      </c>
+      <c r="C13">
+        <v>-15.3101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
+        <v>7.9465000000000003</v>
+      </c>
+      <c r="C14">
+        <v>-1.0232000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15">
+        <v>39.074199999999998</v>
+      </c>
+      <c r="C15">
+        <v>21.824300000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>15.7835</v>
+      </c>
+      <c r="C16">
+        <v>-90.230800000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17">
+        <v>9.9456000000000007</v>
+      </c>
+      <c r="C17">
+        <v>-9.6966000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18">
+        <v>11.803699999999999</v>
+      </c>
+      <c r="C18">
+        <v>-15.180400000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19">
+        <v>1.6508</v>
+      </c>
+      <c r="C19">
+        <v>10.267899999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20">
+        <v>15.2</v>
+      </c>
+      <c r="C20">
+        <v>-86.241900000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21">
+        <v>20.593699999999998</v>
+      </c>
+      <c r="C21">
+        <v>78.962900000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22">
+        <v>-2.3599999999999999E-2</v>
+      </c>
+      <c r="C22">
+        <v>37.906199999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23">
+        <v>33.854700000000001</v>
+      </c>
+      <c r="C23">
+        <v>35.862299999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24">
+        <v>6.4280999999999997</v>
+      </c>
+      <c r="C24">
+        <v>-9.4295000000000009</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25">
+        <v>-18.7669</v>
+      </c>
+      <c r="C25">
+        <v>46.869100000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>-13.254300000000001</v>
+      </c>
+      <c r="C26">
+        <v>34.301499999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27">
+        <v>17.570699999999999</v>
+      </c>
+      <c r="C27">
+        <v>-3.9962</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28">
+        <v>-18.665700000000001</v>
+      </c>
+      <c r="C28">
+        <v>35.529600000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29">
+        <v>31.952200000000001</v>
+      </c>
+      <c r="C29">
+        <v>35.233199999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30">
+        <v>-9.19</v>
+      </c>
+      <c r="C30">
+        <v>-75.015199999999993</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31">
+        <v>6.6111000000000004</v>
+      </c>
+      <c r="C31">
+        <v>20.939399999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32">
+        <v>-4.0382999999999996</v>
+      </c>
+      <c r="C32">
+        <v>21.758700000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33">
+        <v>18.735700000000001</v>
+      </c>
+      <c r="C33">
+        <v>-70.162700000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34">
+        <v>14.497400000000001</v>
+      </c>
+      <c r="C34">
+        <v>-14.452400000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35">
+        <v>8.4605999999999995</v>
+      </c>
+      <c r="C35">
+        <v>-11.7799</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36">
+        <v>34.802100000000003</v>
+      </c>
+      <c r="C36">
+        <v>38.9968</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37">
+        <v>-6.3689999999999998</v>
+      </c>
+      <c r="C37">
+        <v>34.888800000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38">
+        <v>8.6195000000000004</v>
+      </c>
+      <c r="C38">
+        <v>0.82479999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39">
+        <v>48.379399999999997</v>
+      </c>
+      <c r="C39">
+        <v>31.165600000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40">
+        <v>1.3733</v>
+      </c>
+      <c r="C40">
+        <v>32.290300000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41">
+        <v>-32.522799999999997</v>
+      </c>
+      <c r="C41">
+        <v>-55.765799999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42">
+        <v>6.4238</v>
+      </c>
+      <c r="C42">
+        <v>-66.589699999999993</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43">
+        <v>14.058299999999999</v>
+      </c>
+      <c r="C43">
+        <v>108.27719999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Historical_data_AC.xlsx
+++ b/Historical_data_AC.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6450e5a01e7561fa/Desktop/ONG_proyectopersonal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{98D57DAD-A366-43BE-B74E-2A6B22B12204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{8048F2C6-EA20-42D2-B1B5-56F92122D20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{34D6BA04-1AFF-4A7C-9B19-3A12058CBEFE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{34D6BA04-1AFF-4A7C-9B19-3A12058CBEFE}"/>
   </bookViews>
   <sheets>
     <sheet name="All containers" sheetId="1" r:id="rId1"/>
     <sheet name="Material" sheetId="2" r:id="rId2"/>
-    <sheet name="Countries coordinates" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="55">
   <si>
     <t>Numero Contenedor</t>
   </si>
@@ -207,25 +206,21 @@
   <si>
     <t>Material enviado</t>
   </si>
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>Latitude</t>
-  </si>
-  <si>
-    <t>Longitude</t>
-  </si>
-  <si>
-    <t>Perú</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -241,7 +236,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -249,12 +244,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -270,6 +297,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -597,13 +628,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5745,30 +5776,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="3">
         <v>2020</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="3">
         <v>2021</v>
       </c>
-      <c r="D1">
+      <c r="D1" s="3">
         <v>2022</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="3">
         <v>2023</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="3">
         <v>2024</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="3">
         <v>2025</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D2">
@@ -5785,7 +5816,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D3">
@@ -5802,7 +5833,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B4">
@@ -5825,7 +5856,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D5">
@@ -5842,7 +5873,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D6">
@@ -5859,7 +5890,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B7">
@@ -5882,7 +5913,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D8">
@@ -5899,7 +5930,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C9">
@@ -5919,7 +5950,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C10">
@@ -5936,489 +5967,6 @@
       </c>
       <c r="G10">
         <v>71</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE55D653-3B6D-48C5-A45F-119C8615AE3D}">
-  <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
-        <v>-8.8390000000000004</v>
-      </c>
-      <c r="C2">
-        <v>13.289400000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3">
-        <v>28.033899999999999</v>
-      </c>
-      <c r="C3">
-        <v>1.6596</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>9.3077000000000005</v>
-      </c>
-      <c r="C4">
-        <v>2.3157999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
-        <v>12.238300000000001</v>
-      </c>
-      <c r="C5">
-        <v>-1.5616000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6">
-        <v>-3.3731</v>
-      </c>
-      <c r="C6">
-        <v>29.918900000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>16.538799999999998</v>
-      </c>
-      <c r="C7">
-        <v>-23.041799999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>7.3696999999999999</v>
-      </c>
-      <c r="C8">
-        <v>12.354699999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9">
-        <v>-0.22800000000000001</v>
-      </c>
-      <c r="C9">
-        <v>15.8277</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10">
-        <v>21.521799999999999</v>
-      </c>
-      <c r="C10">
-        <v>-77.781199999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11">
-        <v>40.463700000000003</v>
-      </c>
-      <c r="C11">
-        <v>-3.7492000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12">
-        <v>9.1449999999999996</v>
-      </c>
-      <c r="C12">
-        <v>40.489699999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13">
-        <v>13.443199999999999</v>
-      </c>
-      <c r="C13">
-        <v>-15.3101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14">
-        <v>7.9465000000000003</v>
-      </c>
-      <c r="C14">
-        <v>-1.0232000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15">
-        <v>39.074199999999998</v>
-      </c>
-      <c r="C15">
-        <v>21.824300000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16">
-        <v>15.7835</v>
-      </c>
-      <c r="C16">
-        <v>-90.230800000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17">
-        <v>9.9456000000000007</v>
-      </c>
-      <c r="C17">
-        <v>-9.6966000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18">
-        <v>11.803699999999999</v>
-      </c>
-      <c r="C18">
-        <v>-15.180400000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19">
-        <v>1.6508</v>
-      </c>
-      <c r="C19">
-        <v>10.267899999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20">
-        <v>15.2</v>
-      </c>
-      <c r="C20">
-        <v>-86.241900000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21">
-        <v>20.593699999999998</v>
-      </c>
-      <c r="C21">
-        <v>78.962900000000005</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22">
-        <v>-2.3599999999999999E-2</v>
-      </c>
-      <c r="C22">
-        <v>37.906199999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23">
-        <v>33.854700000000001</v>
-      </c>
-      <c r="C23">
-        <v>35.862299999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24">
-        <v>6.4280999999999997</v>
-      </c>
-      <c r="C24">
-        <v>-9.4295000000000009</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25">
-        <v>-18.7669</v>
-      </c>
-      <c r="C25">
-        <v>46.869100000000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26">
-        <v>-13.254300000000001</v>
-      </c>
-      <c r="C26">
-        <v>34.301499999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27">
-        <v>17.570699999999999</v>
-      </c>
-      <c r="C27">
-        <v>-3.9962</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28">
-        <v>-18.665700000000001</v>
-      </c>
-      <c r="C28">
-        <v>35.529600000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29">
-        <v>31.952200000000001</v>
-      </c>
-      <c r="C29">
-        <v>35.233199999999997</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30">
-        <v>-9.19</v>
-      </c>
-      <c r="C30">
-        <v>-75.015199999999993</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31">
-        <v>6.6111000000000004</v>
-      </c>
-      <c r="C31">
-        <v>20.939399999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32">
-        <v>-4.0382999999999996</v>
-      </c>
-      <c r="C32">
-        <v>21.758700000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33">
-        <v>18.735700000000001</v>
-      </c>
-      <c r="C33">
-        <v>-70.162700000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34">
-        <v>14.497400000000001</v>
-      </c>
-      <c r="C34">
-        <v>-14.452400000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35">
-        <v>8.4605999999999995</v>
-      </c>
-      <c r="C35">
-        <v>-11.7799</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36">
-        <v>34.802100000000003</v>
-      </c>
-      <c r="C36">
-        <v>38.9968</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37">
-        <v>-6.3689999999999998</v>
-      </c>
-      <c r="C37">
-        <v>34.888800000000003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38">
-        <v>8.6195000000000004</v>
-      </c>
-      <c r="C38">
-        <v>0.82479999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39">
-        <v>48.379399999999997</v>
-      </c>
-      <c r="C39">
-        <v>31.165600000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40">
-        <v>1.3733</v>
-      </c>
-      <c r="C40">
-        <v>32.290300000000002</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41">
-        <v>-32.522799999999997</v>
-      </c>
-      <c r="C41">
-        <v>-55.765799999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42">
-        <v>6.4238</v>
-      </c>
-      <c r="C42">
-        <v>-66.589699999999993</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43">
-        <v>14.058299999999999</v>
-      </c>
-      <c r="C43">
-        <v>108.27719999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Historical_data_AC.xlsx
+++ b/Historical_data_AC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6450e5a01e7561fa/Desktop/ONG_proyectopersonal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{8048F2C6-EA20-42D2-B1B5-56F92122D20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B971A0C7-A9A2-489A-9AF6-E91293DE05CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{34D6BA04-1AFF-4A7C-9B19-3A12058CBEFE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="56">
   <si>
     <t>Numero Contenedor</t>
   </si>
@@ -206,6 +206,9 @@
   <si>
     <t>Material enviado</t>
   </si>
+  <si>
+    <t>Placas solares</t>
+  </si>
 </sst>
 </file>
 
@@ -277,11 +280,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -297,10 +302,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -620,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DDCD075-27BE-40FA-AF83-D2B889D59367}">
-  <dimension ref="A1:C428"/>
+  <dimension ref="A1:C430"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -5761,6 +5762,28 @@
         <v>2025</v>
       </c>
     </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A429">
+        <v>428</v>
+      </c>
+      <c r="B429" t="s">
+        <v>33</v>
+      </c>
+      <c r="C429">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A430">
+        <v>429</v>
+      </c>
+      <c r="B430" t="s">
+        <v>33</v>
+      </c>
+      <c r="C430">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5769,13 +5792,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08F25E9B-6CE3-43D0-A02E-D9AB00F89E94}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>54</v>
       </c>
@@ -5797,8 +5820,11 @@
       <c r="G1" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="5">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
@@ -5814,8 +5840,11 @@
       <c r="G2">
         <v>156</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>46</v>
       </c>
@@ -5832,7 +5861,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>47</v>
       </c>
@@ -5855,7 +5884,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>48</v>
       </c>
@@ -5872,7 +5901,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>49</v>
       </c>
@@ -5889,7 +5918,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>50</v>
       </c>
@@ -5912,7 +5941,7 @@
         <v>601928</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>51</v>
       </c>
@@ -5929,7 +5958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
@@ -5949,7 +5978,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>53</v>
       </c>
@@ -5967,6 +5996,20 @@
       </c>
       <c r="G10">
         <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
